--- a/data/trans_orig/IQ21A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ21A-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de veces que han estado hospitalizados a lo largo de estos últimos 12 meses</t>
+          <t>Menores según el número de veces que han estado hospitalizados a lo largo de estos últimos 12 meses (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,37</t>
+          <t>1,0; 3,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,61</t>
+          <t>1,0; 1,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,11</t>
+          <t>1,11; 3,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,83</t>
+          <t>1,08; 1,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,3</t>
+          <t>1,0; 2,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,96</t>
+          <t>1,12; 1,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,67</t>
+          <t>1,0; 1,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,32</t>
+          <t>1,0; 1,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,4</t>
+          <t>1,0; 1,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,6</t>
+          <t>1,0; 1,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,67</t>
+          <t>1,0; 1,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,44</t>
+          <t>1,0; 1,58</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 39,27</t>
+          <t>1,23; 39,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,57</t>
+          <t>1,0; 1,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,43</t>
+          <t>1,0; 1,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,89</t>
+          <t>1,0; 5,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,35</t>
+          <t>1,0; 1,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,94</t>
+          <t>1,0; 2,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,34</t>
+          <t>1,0; 2,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,24</t>
+          <t>1,13; 4,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,64</t>
+          <t>1,0; 1,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,62</t>
+          <t>1,08; 3,1</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,4</t>
+          <t>1,0; 1,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1836,17 +1836,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,23</t>
+          <t>1,0; 1,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,26</t>
+          <t>1,05; 1,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,37</t>
+          <t>1,07; 1,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,76</t>
+          <t>1,06; 1,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,51</t>
+          <t>1,08; 1,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,71</t>
+          <t>1,09; 11,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,41</t>
+          <t>1,05; 1,38</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,23</t>
+          <t>1,16; 5,86</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">

--- a/data/trans_orig/IQ21A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ21A-Provincia-trans_orig.xlsx
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,35</t>
+          <t>1,0; 3,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,67</t>
+          <t>1,0; 1,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,27</t>
+          <t>1,0; 3,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,78</t>
+          <t>1,08; 1,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,39</t>
+          <t>1,0; 2,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,38</t>
+          <t>1,0; 1,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,93</t>
+          <t>1,11; 1,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,65</t>
+          <t>1,0; 1,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,38</t>
+          <t>1,0; 1,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,65</t>
+          <t>1,0; 1,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,39</t>
+          <t>1,0; 1,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,56</t>
+          <t>1,0; 1,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,68</t>
+          <t>1,0; 1,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 39,27</t>
+          <t>1,0; 39,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,54</t>
+          <t>1,0; 1,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,44</t>
+          <t>1,0; 1,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,34</t>
+          <t>1,0; 1,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,84</t>
+          <t>1,0; 2,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,37</t>
+          <t>1,0; 2,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,16</t>
+          <t>1,13; 4,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,63</t>
+          <t>1,0; 1,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,1</t>
+          <t>1,08; 3,54</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,2</t>
+          <t>1,0; 1,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,36</t>
+          <t>1,07; 1,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,62</t>
+          <t>1,06; 1,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,54</t>
+          <t>1,1; 1,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 11,27</t>
+          <t>1,12; 11,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1876,17 +1876,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,38</t>
+          <t>1,04; 1,4</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,35</t>
+          <t>1,09; 1,34</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,86</t>
+          <t>1,15; 6,18</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
